--- a/SGC-CKN/Excel/9a704025-26e8-430e-ab57-bc12ea99935d_Hạng_mục__Trung_tâm_văn_hóa_thể_thao__trung_tâm_hội_nghị__nhà_hát_P_337_D1200_30-03-2026.xlsx
+++ b/SGC-CKN/Excel/9a704025-26e8-430e-ab57-bc12ea99935d_Hạng_mục__Trung_tâm_văn_hóa_thể_thao__trung_tâm_hội_nghị__nhà_hát_P_337_D1200_30-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P.337</t>
+    <t>P337</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
